--- a/job_applications.xlsx
+++ b/job_applications.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,16 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>GitHub Folder Link</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Resume File Name</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Cover Letter File Name</t>
         </is>
       </c>
     </row>
@@ -564,6 +574,8 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +641,8 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -694,6 +708,8 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,6 +775,8 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -824,6 +842,8 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,6 +909,8 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -954,6 +976,8 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1019,6 +1043,8 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1084,6 +1110,8 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1149,6 +1177,8 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1214,6 +1244,8 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1279,6 +1311,8 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1344,6 +1378,8 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1409,6 +1445,8 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1474,6 +1512,8 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1539,6 +1579,8 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1604,6 +1646,8 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1669,6 +1713,8 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1734,6 +1780,8 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1799,6 +1847,8 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1864,6 +1914,8 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1929,6 +1981,8 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1994,6 +2048,8 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2059,6 +2115,8 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2124,6 +2182,8 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2189,6 +2249,8 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2254,6 +2316,8 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2319,6 +2383,8 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2384,6 +2450,8 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2449,6 +2517,8 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2509,6 +2579,762 @@
           <t>https://github.com/Pokedash01/job-hunter/tree/main/generated_docs</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Production Supervisor (GYM &amp; Fitness Equipments)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Koxtons Sports</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>UP, IN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=fc3f5547efa74ef8</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Resume_Koxtons_Sports_Production_Supe_20260830_130945.pdf</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CoverLetter_Koxtons_Sports_Production_Supe_20260830_130945.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Operation cum Production Manager</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Koxtons Sports</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UP, IN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=9c37571188660300</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Resume_Koxtons_Sports_Operation_cum_P_20260830_130948.pdf</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CoverLetter_Koxtons_Sports_Operation_cum_P_20260830_130948.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Regional Operations Manager</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Good Flippin Burger</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DL, IN</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=55d106a3557bd10b</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Resume_Good_Flippin_Bu_Regional_Operat_20260830_130951.pdf</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CoverLetter_Good_Flippin_Bu_Regional_Operat_20260830_130951.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Area Operations Manager</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Good Flippin Burger</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MH, IN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://in.indeed.com/viewjob?jk=f1b0c136bc26953a</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Resume_Good_Flippin_Bu_Area_Operations_20260830_130953.pdf</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CoverLetter_Good_Flippin_Bu_Area_Operations_20260830_130953.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lead, Power Platform</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Kenvue</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4449215742</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Resume_Kenvue_Lead__Power_Pla_20260830_130956.pdf</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CoverLetter_Kenvue_Lead__Power_Pla_20260830_130956.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Manager, D&amp;T, Process Automation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dsm-firmenich</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4347442998</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Resume_dsm_firmenich_Manager__D_T__P_20260830_130959.pdf</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CoverLetter_dsm_firmenich_Manager__D_T__P_20260830_130959.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DWP Solution Consultant</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TECEZE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4459732214</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Resume_TECEZE_DWP_Solution_Co_20260830_131002.pdf</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CoverLetter_TECEZE_DWP_Solution_Co_20260830_131002.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BPI - Analyst</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IFF</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4414911972</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Resume_IFF_BPI___Analyst_20260830_131004.pdf</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>CoverLetter_IFF_BPI___Analyst_20260830_131004.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AI Council Program Manager &amp; PMO Lead</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>algoleap</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4439217366</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Resume_algoleap_AI_Council_Prog_20260830_131007.pdf</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CoverLetter_algoleap_AI_Council_Prog_20260830_131007.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lead Business Execution Consultant</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451071162</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Resume_Wells_Fargo_Lead_Business_E_20260830_131011.pdf</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CoverLetter_Wells_Fargo_Lead_Business_E_20260830_131011.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Field Platforms Operations Lead</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sanofi</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4451076156</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Resume_Sanofi_Field_Platforms_20260830_131014.pdf</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CoverLetter_Sanofi_Field_Platforms_20260830_131014.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Technical Partner Manager</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nexthink</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4432968874</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Resume_Nexthink_Technical_Partn_20260830_131016.pdf</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CoverLetter_Nexthink_Technical_Partn_20260830_131016.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-30 13:10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Power Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Consilium Safety Group</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kochi, Kerala, India</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Meets/Exceeds Location Threshold</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4440776203</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PDFs Attached in Telegram / Saved in Repo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Resume_Consilium_Safet_Power_Platform__20260830_131019.pdf</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CoverLetter_Consilium_Safet_Power_Platform__20260830_131019.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
